--- a/output/pdf_financials_xlsx/KALO.xlsx
+++ b/output/pdf_financials_xlsx/KALO.xlsx
@@ -3065,22 +3065,22 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>6.175469</v>
+        <v>6.395619</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>6.175469</v>
+        <v>7.15471</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>6.175469</v>
+        <v>7.31268</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>6.175469</v>
+        <v>8.537558000000001</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>6.175469</v>
+        <v>8.766662</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>6.175469</v>
+        <v>9.577149</v>
       </c>
     </row>
     <row r="93">
@@ -5032,7 +5032,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -5808,7 +5812,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -6463,7 +6471,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KALO.xlsx
+++ b/output/pdf_financials_xlsx/KALO.xlsx
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.005075</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.483766</v>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.005075</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.483766</v>
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000685</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1182,7 +1182,7 @@
         <v>-0.005075</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.483062</v>
+        <v>-0.482377</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-5.874173</v>
@@ -1238,7 +1238,7 @@
         <v>-0.005075</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.479946</v>
+        <v>-0.479261</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-5.863287</v>
@@ -1382,25 +1382,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.137425</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.257751</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.420988</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.070608</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.453467</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.192169</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>3.178442</v>
       </c>
     </row>
     <row r="35">
@@ -1438,25 +1438,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.137425</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.257751</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.420988</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.070608</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.453467</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.192169</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>3.178442</v>
       </c>
     </row>
     <row r="37">
@@ -1774,25 +1774,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.147425</v>
+        <v>0.01</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.255583</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.567977</v>
+        <v>0.146989</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.260495</v>
+        <v>0.189887</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.504605</v>
+        <v>0.051138</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.312764</v>
+        <v>0.120595</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.751692</v>
+        <v>0.57325</v>
       </c>
     </row>
     <row r="49">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E202" s="5" t="n">

--- a/output/pdf_financials_xlsx/KALO.xlsx
+++ b/output/pdf_financials_xlsx/KALO.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>7.499999999999999e-05</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.016449</v>
@@ -2330,19 +2330,19 @@
         <v>0.006</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.103122</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.286668</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.08893</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.118169</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.215626</v>
       </c>
     </row>
     <row r="68">
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002168</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -3438,7 +3438,7 @@
         <v>0.005</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.037104</v>
+        <v>0.034936</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.167904</v>
@@ -3578,13 +3578,13 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007558</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.058901</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.110728</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.184222</v>
       </c>
     </row>
     <row r="112">
@@ -4264,13 +4264,13 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007558</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.058901</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.110728</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -4279,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.184222</v>
       </c>
     </row>
     <row r="135">
@@ -4292,13 +4292,13 @@
         <v>-0.010075</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.187079</v>
+        <v>-0.194637</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-2.827883</v>
+        <v>-2.886784</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-2.096499</v>
+        <v>-2.207227</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-1.574669</v>
@@ -4307,7 +4307,7 @@
         <v>-0.796892</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-3.124004</v>
+        <v>-3.308226</v>
       </c>
     </row>
   </sheetData>
@@ -7916,7 +7916,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -8621,7 +8625,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -9929,7 +9937,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -10845,7 +10857,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -14078,7 +14094,11 @@
           <t>Office expenses $</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E197" s="5" t="n">
         <v>7.499999999999999e-05</v>
       </c>
